--- a/public/template-scan-import.xlsx
+++ b/public/template-scan-import.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="scans" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,37 +413,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>เลขสแกนนิ้ว</t>
+          <t>ลำดับนิ้วมือ</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>คำนำหน้า</t>
+          <t>รหัสนิ้วมือ</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>ชื่อ</t>
+          <t>ชื่อ-สกุล</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>นามสกุล</t>
+          <t>Auto-Assign</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -453,34 +457,45 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>กะการทำงาน</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>เวลาเข้า</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>เวลาออก</t>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>เวลาเลิก</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>เข้างาน</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ออกงาน</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Department</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>นาย</t>
-        </is>
+      <c r="A2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1201</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>สมชาย</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ใจดี</t>
+          <t>ประทิน  สะแม</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -490,34 +505,45 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>Daytime</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ส่วนงานพืชผัก/สวนครัว</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>นาย</t>
-        </is>
+      <c r="A3" t="n">
+        <v>107</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1201</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>สมชาย</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ใจดี</t>
+          <t>ประทิน  สะแม</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -527,12 +553,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>Daytime</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ส่วนงานพืชผัก/สวนครัว</t>
         </is>
       </c>
     </row>
